--- a/insights/20251230-20241230-insights/Comparison_Payroll.xlsx
+++ b/insights/20251230-20241230-insights/Comparison_Payroll.xlsx
@@ -19,306 +19,306 @@
     <t>eecode</t>
   </si>
   <si>
+    <t>B884</t>
+  </si>
+  <si>
+    <t>G891</t>
+  </si>
+  <si>
+    <t>A1K3</t>
+  </si>
+  <si>
+    <t>D528</t>
+  </si>
+  <si>
+    <t>D521</t>
+  </si>
+  <si>
+    <t>J405</t>
+  </si>
+  <si>
+    <t>F627</t>
+  </si>
+  <si>
+    <t>A4BY</t>
+  </si>
+  <si>
+    <t>A3ML</t>
+  </si>
+  <si>
+    <t>A2CL</t>
+  </si>
+  <si>
+    <t>I304</t>
+  </si>
+  <si>
+    <t>A31F</t>
+  </si>
+  <si>
+    <t>A2C3</t>
+  </si>
+  <si>
     <t>D816</t>
   </si>
   <si>
-    <t>A31F</t>
-  </si>
-  <si>
-    <t>I304</t>
-  </si>
-  <si>
-    <t>D521</t>
-  </si>
-  <si>
-    <t>D528</t>
-  </si>
-  <si>
-    <t>J405</t>
-  </si>
-  <si>
-    <t>A1K3</t>
-  </si>
-  <si>
-    <t>G891</t>
+    <t>C282</t>
+  </si>
+  <si>
+    <t>A337</t>
+  </si>
+  <si>
+    <t>A749</t>
+  </si>
+  <si>
+    <t>H632</t>
+  </si>
+  <si>
+    <t>D954</t>
+  </si>
+  <si>
+    <t>E483</t>
+  </si>
+  <si>
+    <t>H352</t>
   </si>
   <si>
     <t>G693</t>
   </si>
   <si>
-    <t>A2C3</t>
-  </si>
-  <si>
-    <t>H632</t>
-  </si>
-  <si>
-    <t>A337</t>
-  </si>
-  <si>
-    <t>A3ML</t>
-  </si>
-  <si>
-    <t>C282</t>
-  </si>
-  <si>
-    <t>F627</t>
-  </si>
-  <si>
-    <t>A4BY</t>
-  </si>
-  <si>
-    <t>A749</t>
-  </si>
-  <si>
-    <t>B884</t>
-  </si>
-  <si>
-    <t>D954</t>
-  </si>
-  <si>
-    <t>A2CL</t>
-  </si>
-  <si>
-    <t>E483</t>
-  </si>
-  <si>
-    <t>H352</t>
+    <t>B221</t>
+  </si>
+  <si>
+    <t>I384</t>
   </si>
   <si>
     <t>A3J5</t>
   </si>
   <si>
-    <t>B221</t>
-  </si>
-  <si>
-    <t>I384</t>
+    <t>A3IP</t>
+  </si>
+  <si>
+    <t>E568</t>
+  </si>
+  <si>
+    <t>A35Y</t>
+  </si>
+  <si>
+    <t>A0QH</t>
   </si>
   <si>
     <t>A3IC</t>
   </si>
   <si>
+    <t>A3KD</t>
+  </si>
+  <si>
+    <t>A3WC</t>
+  </si>
+  <si>
+    <t>A3J1</t>
+  </si>
+  <si>
     <t>A3IH</t>
   </si>
   <si>
-    <t>A3J1</t>
-  </si>
-  <si>
-    <t>E568</t>
-  </si>
-  <si>
-    <t>A35Y</t>
-  </si>
-  <si>
-    <t>A3IP</t>
+    <t>A0QK</t>
   </si>
   <si>
     <t>J561</t>
   </si>
   <si>
-    <t>A0QK</t>
-  </si>
-  <si>
     <t>A42T</t>
   </si>
   <si>
-    <t>A0QH</t>
-  </si>
-  <si>
-    <t>A3WC</t>
-  </si>
-  <si>
-    <t>A3KD</t>
-  </si>
-  <si>
     <t>F703</t>
   </si>
   <si>
+    <t>F497</t>
+  </si>
+  <si>
     <t>F035</t>
   </si>
   <si>
-    <t>F497</t>
+    <t>G963</t>
+  </si>
+  <si>
+    <t>B896</t>
+  </si>
+  <si>
+    <t>C349</t>
   </si>
   <si>
     <t>C215</t>
   </si>
   <si>
-    <t>C349</t>
-  </si>
-  <si>
-    <t>B896</t>
-  </si>
-  <si>
-    <t>G963</t>
-  </si>
-  <si>
     <t>B567</t>
   </si>
   <si>
     <t>A20A</t>
   </si>
   <si>
+    <t>G381</t>
+  </si>
+  <si>
+    <t>A661</t>
+  </si>
+  <si>
+    <t>H115</t>
+  </si>
+  <si>
+    <t>G573</t>
+  </si>
+  <si>
+    <t>A3I5</t>
+  </si>
+  <si>
+    <t>A382</t>
+  </si>
+  <si>
+    <t>A3HX</t>
+  </si>
+  <si>
+    <t>A32C</t>
+  </si>
+  <si>
+    <t>A170</t>
+  </si>
+  <si>
+    <t>G190</t>
+  </si>
+  <si>
+    <t>F124</t>
+  </si>
+  <si>
+    <t>E791</t>
+  </si>
+  <si>
+    <t>E660</t>
+  </si>
+  <si>
+    <t>D619</t>
+  </si>
+  <si>
+    <t>E893</t>
+  </si>
+  <si>
+    <t>E835</t>
+  </si>
+  <si>
     <t>C644</t>
   </si>
   <si>
-    <t>A170</t>
-  </si>
-  <si>
-    <t>A3HX</t>
-  </si>
-  <si>
-    <t>A32C</t>
-  </si>
-  <si>
-    <t>H115</t>
-  </si>
-  <si>
-    <t>G573</t>
-  </si>
-  <si>
-    <t>A661</t>
-  </si>
-  <si>
-    <t>D619</t>
-  </si>
-  <si>
-    <t>E893</t>
-  </si>
-  <si>
-    <t>A3I5</t>
-  </si>
-  <si>
-    <t>G381</t>
-  </si>
-  <si>
-    <t>E835</t>
-  </si>
-  <si>
-    <t>A382</t>
-  </si>
-  <si>
-    <t>G190</t>
-  </si>
-  <si>
-    <t>F124</t>
-  </si>
-  <si>
-    <t>E791</t>
-  </si>
-  <si>
-    <t>E660</t>
+    <t>A3VD</t>
+  </si>
+  <si>
+    <t>A3RR</t>
+  </si>
+  <si>
+    <t>A4FO</t>
+  </si>
+  <si>
+    <t>A2FB</t>
+  </si>
+  <si>
+    <t>A3X6</t>
+  </si>
+  <si>
+    <t>A0ZW</t>
+  </si>
+  <si>
+    <t>A2FK</t>
+  </si>
+  <si>
+    <t>A3RQ</t>
+  </si>
+  <si>
+    <t>A2CT</t>
+  </si>
+  <si>
+    <t>F959</t>
+  </si>
+  <si>
+    <t>A2CR</t>
+  </si>
+  <si>
+    <t>A3T9</t>
   </si>
   <si>
     <t>A0TR</t>
   </si>
   <si>
+    <t>F510</t>
+  </si>
+  <si>
+    <t>J447</t>
+  </si>
+  <si>
     <t>A0QI</t>
   </si>
   <si>
-    <t>F959</t>
-  </si>
-  <si>
-    <t>A3X6</t>
-  </si>
-  <si>
-    <t>A0ZW</t>
-  </si>
-  <si>
-    <t>A3VD</t>
-  </si>
-  <si>
-    <t>A3RR</t>
-  </si>
-  <si>
-    <t>A2CT</t>
-  </si>
-  <si>
-    <t>A4FO</t>
-  </si>
-  <si>
-    <t>A2FK</t>
-  </si>
-  <si>
-    <t>J447</t>
-  </si>
-  <si>
-    <t>F510</t>
-  </si>
-  <si>
-    <t>A3T9</t>
-  </si>
-  <si>
-    <t>A3RQ</t>
-  </si>
-  <si>
-    <t>A2CR</t>
-  </si>
-  <si>
-    <t>A2FB</t>
+    <t>A2XG</t>
+  </si>
+  <si>
+    <t>A399</t>
   </si>
   <si>
     <t>E190</t>
   </si>
   <si>
-    <t>A2XG</t>
-  </si>
-  <si>
     <t>G730</t>
   </si>
   <si>
-    <t>A399</t>
-  </si>
-  <si>
     <t>H439</t>
   </si>
   <si>
+    <t>A1F9</t>
+  </si>
+  <si>
+    <t>A3UU</t>
+  </si>
+  <si>
+    <t>A3RO</t>
+  </si>
+  <si>
+    <t>A2ID</t>
+  </si>
+  <si>
+    <t>A3RK</t>
+  </si>
+  <si>
+    <t>A2I3</t>
+  </si>
+  <si>
     <t>A2PL</t>
   </si>
   <si>
-    <t>A2I3</t>
+    <t>A3O3</t>
+  </si>
+  <si>
+    <t>A4FN</t>
+  </si>
+  <si>
+    <t>A2JE</t>
+  </si>
+  <si>
+    <t>A2YQ</t>
+  </si>
+  <si>
+    <t>A3II</t>
+  </si>
+  <si>
+    <t>A46N</t>
+  </si>
+  <si>
+    <t>A2BQ</t>
   </si>
   <si>
     <t>A30J</t>
   </si>
   <si>
-    <t>A2JE</t>
-  </si>
-  <si>
-    <t>A46N</t>
-  </si>
-  <si>
-    <t>A3RO</t>
-  </si>
-  <si>
-    <t>A2ID</t>
-  </si>
-  <si>
-    <t>A3RK</t>
-  </si>
-  <si>
-    <t>A1F9</t>
-  </si>
-  <si>
-    <t>A3UU</t>
-  </si>
-  <si>
     <t>A11F</t>
   </si>
   <si>
-    <t>A2BQ</t>
-  </si>
-  <si>
-    <t>A3II</t>
-  </si>
-  <si>
-    <t>A2YQ</t>
-  </si>
-  <si>
-    <t>A4FN</t>
-  </si>
-  <si>
-    <t>A3O3</t>
-  </si>
-  <si>
     <t>A0IF</t>
   </si>
   <si>
@@ -328,127 +328,139 @@
     <t>A3KP</t>
   </si>
   <si>
+    <t>A2LG</t>
+  </si>
+  <si>
+    <t>A3KA</t>
+  </si>
+  <si>
     <t>A3XF</t>
   </si>
   <si>
     <t>A0LC</t>
   </si>
   <si>
-    <t>A3KA</t>
-  </si>
-  <si>
-    <t>A2LG</t>
-  </si>
-  <si>
     <t>G605</t>
   </si>
   <si>
+    <t>A3JQ</t>
+  </si>
+  <si>
     <t>A3J4</t>
   </si>
   <si>
+    <t>A0TT</t>
+  </si>
+  <si>
+    <t>I588</t>
+  </si>
+  <si>
     <t>A0H4</t>
   </si>
   <si>
+    <t>A3YJ</t>
+  </si>
+  <si>
+    <t>A3YI</t>
+  </si>
+  <si>
+    <t>A41H</t>
+  </si>
+  <si>
+    <t>E794</t>
+  </si>
+  <si>
+    <t>A3KG</t>
+  </si>
+  <si>
     <t>A41F</t>
   </si>
   <si>
-    <t>A41H</t>
-  </si>
-  <si>
-    <t>A3JQ</t>
-  </si>
-  <si>
-    <t>A3YI</t>
-  </si>
-  <si>
-    <t>A0TT</t>
-  </si>
-  <si>
-    <t>I588</t>
-  </si>
-  <si>
-    <t>A3YJ</t>
-  </si>
-  <si>
-    <t>E794</t>
-  </si>
-  <si>
-    <t>A3KG</t>
+    <t>A2KF</t>
+  </si>
+  <si>
+    <t>A3Z8</t>
+  </si>
+  <si>
+    <t>A3TO</t>
+  </si>
+  <si>
+    <t>A3UE</t>
+  </si>
+  <si>
+    <t>H636</t>
+  </si>
+  <si>
+    <t>A3I6</t>
+  </si>
+  <si>
+    <t>A48R</t>
+  </si>
+  <si>
+    <t>A4DP</t>
+  </si>
+  <si>
+    <t>B2UZ</t>
+  </si>
+  <si>
+    <t>A3YX</t>
+  </si>
+  <si>
+    <t>A3YQ</t>
+  </si>
+  <si>
+    <t>C926</t>
+  </si>
+  <si>
+    <t>A3Z0</t>
   </si>
   <si>
     <t>A3TQ</t>
   </si>
   <si>
-    <t>A3Z0</t>
-  </si>
-  <si>
-    <t>C926</t>
-  </si>
-  <si>
-    <t>A2KF</t>
-  </si>
-  <si>
-    <t>A3TO</t>
-  </si>
-  <si>
-    <t>A3I6</t>
-  </si>
-  <si>
-    <t>A3Z8</t>
+    <t>A0GJ</t>
+  </si>
+  <si>
+    <t>A1H9</t>
+  </si>
+  <si>
+    <t>A45O</t>
+  </si>
+  <si>
+    <t>C913</t>
+  </si>
+  <si>
+    <t>A3TS</t>
+  </si>
+  <si>
+    <t>A0VA</t>
+  </si>
+  <si>
+    <t>A3Z3</t>
+  </si>
+  <si>
+    <t>A3ZC</t>
   </si>
   <si>
     <t>A3GV</t>
   </si>
   <si>
-    <t>A3TS</t>
-  </si>
-  <si>
-    <t>H636</t>
-  </si>
-  <si>
-    <t>A0VA</t>
-  </si>
-  <si>
-    <t>A3Z3</t>
-  </si>
-  <si>
-    <t>A3ZC</t>
-  </si>
-  <si>
-    <t>A48R</t>
-  </si>
-  <si>
-    <t>A0GJ</t>
-  </si>
-  <si>
-    <t>A4DP</t>
-  </si>
-  <si>
-    <t>A3YX</t>
-  </si>
-  <si>
-    <t>B2UZ</t>
-  </si>
-  <si>
-    <t>A3YQ</t>
-  </si>
-  <si>
-    <t>C913</t>
-  </si>
-  <si>
-    <t>A45O</t>
-  </si>
-  <si>
-    <t>A1H9</t>
-  </si>
-  <si>
-    <t>A3UE</t>
+    <t>C213</t>
   </si>
   <si>
     <t>A04U</t>
   </si>
   <si>
-    <t>C213</t>
+    <t>A3YU</t>
+  </si>
+  <si>
+    <t>A4AX</t>
+  </si>
+  <si>
+    <t>A3UH</t>
+  </si>
+  <si>
+    <t>A4DU</t>
   </si>
   <si>
     <t>A515</t>
@@ -457,48 +469,36 @@
     <t>A3Z2</t>
   </si>
   <si>
-    <t>A3UH</t>
-  </si>
-  <si>
-    <t>A4AX</t>
-  </si>
-  <si>
-    <t>A3YU</t>
-  </si>
-  <si>
-    <t>A4DU</t>
-  </si>
-  <si>
     <t>A04Q</t>
   </si>
   <si>
     <t>A2HX</t>
   </si>
   <si>
+    <t>A194</t>
+  </si>
+  <si>
+    <t>A4CZ</t>
+  </si>
+  <si>
     <t>A0J5</t>
   </si>
   <si>
-    <t>A4CZ</t>
-  </si>
-  <si>
-    <t>A194</t>
+    <t>A2WI</t>
+  </si>
+  <si>
+    <t>A4AL</t>
+  </si>
+  <si>
+    <t>A4AF</t>
+  </si>
+  <si>
+    <t>A34P</t>
   </si>
   <si>
     <t>A37Y</t>
   </si>
   <si>
-    <t>A2WI</t>
-  </si>
-  <si>
-    <t>A4AL</t>
-  </si>
-  <si>
-    <t>A34P</t>
-  </si>
-  <si>
-    <t>A4AF</t>
-  </si>
-  <si>
     <t>F025</t>
   </si>
   <si>
@@ -508,25 +508,31 @@
     <t>B035</t>
   </si>
   <si>
+    <t>A3S7</t>
+  </si>
+  <si>
+    <t>A39M</t>
+  </si>
+  <si>
+    <t>A3ON</t>
+  </si>
+  <si>
+    <t>A3PS</t>
+  </si>
+  <si>
+    <t>B322</t>
+  </si>
+  <si>
     <t>C947</t>
   </si>
   <si>
-    <t>A3S7</t>
-  </si>
-  <si>
-    <t>A3ON</t>
-  </si>
-  <si>
-    <t>A3PS</t>
-  </si>
-  <si>
     <t>A2GD</t>
   </si>
   <si>
-    <t>A39M</t>
-  </si>
-  <si>
-    <t>B322</t>
+    <t>A3O6</t>
+  </si>
+  <si>
+    <t>D754</t>
   </si>
   <si>
     <t>H146</t>
@@ -538,43 +544,37 @@
     <t>A0IJ</t>
   </si>
   <si>
-    <t>A3O6</t>
-  </si>
-  <si>
-    <t>D754</t>
-  </si>
-  <si>
     <t>G448</t>
   </si>
   <si>
+    <t>A3TX</t>
+  </si>
+  <si>
+    <t>A2PQ</t>
+  </si>
+  <si>
     <t>A3TY</t>
   </si>
   <si>
-    <t>A2PQ</t>
+    <t>A3TW</t>
   </si>
   <si>
     <t>A2R6</t>
   </si>
   <si>
-    <t>A3TW</t>
-  </si>
-  <si>
-    <t>A3TX</t>
-  </si>
-  <si>
     <t>A415</t>
   </si>
   <si>
     <t>D667</t>
   </si>
   <si>
+    <t>A393</t>
+  </si>
+  <si>
     <t>A2ST</t>
   </si>
   <si>
     <t>A3DQ</t>
-  </si>
-  <si>
-    <t>A393</t>
   </si>
   <si>
     <t>D575</t>
@@ -1201,13 +1201,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46021.33861111111</v>
+        <v>46021.33149305556</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D2" s="2">
-        <v>46021.68800925926</v>
+        <v>46021.70489583333</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>195</v>
@@ -1216,7 +1216,7 @@
         <v>197</v>
       </c>
       <c r="G2" s="2">
-        <v>19.6</v>
+        <v>18.7</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -1233,13 +1233,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.33140046296</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D3" s="2">
-        <v>46021.69890046296</v>
+        <v>46021.70081018518</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>195</v>
@@ -1248,7 +1248,7 @@
         <v>197</v>
       </c>
       <c r="G3" s="2">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
@@ -1265,13 +1265,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>46021.32430555556</v>
+        <v>46021.32769675926</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D4" s="2">
-        <v>46021.72810185186</v>
+        <v>46021.69712962963</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>195</v>
@@ -1280,7 +1280,7 @@
         <v>197</v>
       </c>
       <c r="G4" s="2">
-        <v>23</v>
+        <v>18.6</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
@@ -1297,13 +1297,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>46021.32498842593</v>
+        <v>46021.32336805556</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D5" s="2">
-        <v>46021.70180555555</v>
+        <v>46021.70552083333</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>195</v>
@@ -1312,7 +1312,7 @@
         <v>197</v>
       </c>
       <c r="G5" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H5" s="2">
         <v>0</v>
@@ -1329,13 +1329,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>46021.32336805556</v>
+        <v>46021.32498842593</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D6" s="2">
-        <v>46021.70552083333</v>
+        <v>46021.70180555555</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>195</v>
@@ -1344,7 +1344,7 @@
         <v>197</v>
       </c>
       <c r="G6" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
@@ -1393,22 +1393,18 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>46021.32769675926</v>
+        <v>46021.33077546296</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D8" s="2">
-        <v>46021.69712962963</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
         <v>197</v>
       </c>
       <c r="G8" s="2">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
@@ -1425,13 +1421,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>46021.33140046296</v>
+        <v>46021.33662037037</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D9" s="2">
-        <v>46021.70081018518</v>
+        <v>46021.68881944445</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>195</v>
@@ -1440,7 +1436,7 @@
         <v>197</v>
       </c>
       <c r="G9" s="2">
-        <v>19.6</v>
+        <v>18.35</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
@@ -1457,13 +1453,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>46021.34115740741</v>
+        <v>46021.3244675926</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D10" s="2">
-        <v>46021.70405092592</v>
+        <v>46021.68181712963</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>195</v>
@@ -1489,13 +1485,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>46021.33353009259</v>
+        <v>46021.32745370371</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D11" s="2">
-        <v>46021.70708333333</v>
+        <v>46021.68949074074</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>195</v>
@@ -1504,7 +1500,7 @@
         <v>197</v>
       </c>
       <c r="G11" s="2">
-        <v>19.25</v>
+        <v>18.6</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
@@ -1521,13 +1517,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>46021.32285879629</v>
+        <v>46021.32430555556</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D12" s="2">
-        <v>46021.73335648148</v>
+        <v>46021.72810185186</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>195</v>
@@ -1536,7 +1532,7 @@
         <v>197</v>
       </c>
       <c r="G12" s="2">
-        <v>26.8</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2">
         <v>0</v>
@@ -1553,13 +1549,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>46021.33247685185</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D13" s="2">
-        <v>46021.70076388889</v>
+        <v>46021.69890046296</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>195</v>
@@ -1585,13 +1581,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>46021.3244675926</v>
+        <v>46021.33353009259</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D14" s="2">
-        <v>46021.68181712963</v>
+        <v>46021.70708333333</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>195</v>
@@ -1600,7 +1596,7 @@
         <v>197</v>
       </c>
       <c r="G14" s="2">
-        <v>18.35</v>
+        <v>19.25</v>
       </c>
       <c r="H14" s="2">
         <v>0</v>
@@ -1617,13 +1613,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>46021.32355324074</v>
+        <v>46021.33861111111</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D15" s="2">
-        <v>46021.70134259259</v>
+        <v>46021.68800925926</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>195</v>
@@ -1632,7 +1628,7 @@
         <v>197</v>
       </c>
       <c r="G15" s="2">
-        <v>18.7</v>
+        <v>19.6</v>
       </c>
       <c r="H15" s="2">
         <v>0</v>
@@ -1649,13 +1645,17 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>46021.33077546296</v>
+        <v>46021.32355324074</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="D16" s="2">
+        <v>46021.70134259259</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F16" s="2" t="s">
         <v>197</v>
       </c>
@@ -1677,13 +1677,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>46021.33662037037</v>
+        <v>46021.33247685185</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D17" s="2">
-        <v>46021.68881944445</v>
+        <v>46021.70076388889</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>195</v>
@@ -1692,7 +1692,7 @@
         <v>197</v>
       </c>
       <c r="G17" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H17" s="2">
         <v>0</v>
@@ -1741,13 +1741,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>46021.33149305556</v>
+        <v>46021.32285879629</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D19" s="2">
-        <v>46021.70489583333</v>
+        <v>46021.73335648148</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>195</v>
@@ -1756,7 +1756,7 @@
         <v>197</v>
       </c>
       <c r="G19" s="2">
-        <v>18.7</v>
+        <v>26.8</v>
       </c>
       <c r="H19" s="2">
         <v>0</v>
@@ -1805,13 +1805,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>46021.32745370371</v>
+        <v>46021.32575231481</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D21" s="2">
-        <v>46021.68949074074</v>
+        <v>46021.6834375</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>195</v>
@@ -1820,7 +1820,7 @@
         <v>197</v>
       </c>
       <c r="G21" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H21" s="2">
         <v>0</v>
@@ -1837,13 +1837,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>46021.32575231481</v>
+        <v>46021.32677083334</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D22" s="2">
-        <v>46021.6834375</v>
+        <v>46021.70348379629</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>195</v>
@@ -1852,7 +1852,7 @@
         <v>197</v>
       </c>
       <c r="G22" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H22" s="2">
         <v>0</v>
@@ -1869,13 +1869,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>46021.32677083334</v>
+        <v>46021.34115740741</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D23" s="2">
-        <v>46021.70348379629</v>
+        <v>46021.70405092592</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>195</v>
@@ -1884,7 +1884,7 @@
         <v>197</v>
       </c>
       <c r="G23" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H23" s="2">
         <v>0</v>
@@ -1901,13 +1901,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>46021.28842592592</v>
+        <v>46021.29054398148</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D24" s="2">
-        <v>46021.72347222222</v>
+        <v>46021.72282407407</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>195</v>
@@ -1916,7 +1916,7 @@
         <v>198</v>
       </c>
       <c r="G24" s="2">
-        <v>20.2</v>
+        <v>27</v>
       </c>
       <c r="H24" s="2">
         <v>0</v>
@@ -1933,13 +1933,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>46021.29054398148</v>
+        <v>46021.29010416667</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D25" s="2">
-        <v>46021.72282407407</v>
+        <v>46021.72649305555</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>195</v>
@@ -1965,13 +1965,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>46021.29010416667</v>
+        <v>46021.28842592592</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D26" s="2">
-        <v>46021.72649305555</v>
+        <v>46021.72347222222</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>195</v>
@@ -1980,7 +1980,7 @@
         <v>198</v>
       </c>
       <c r="G26" s="2">
-        <v>27</v>
+        <v>20.2</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
@@ -1997,22 +1997,18 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>46021.49179398148</v>
+        <v>46021.98780092593</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D27" s="2">
-        <v>46021.60519675926</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
         <v>199</v>
       </c>
       <c r="G27" s="2">
-        <v>20.2</v>
+        <v>23</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
@@ -2029,13 +2025,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>46021.49797453704</v>
+        <v>46021.32273148148</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D28" s="2">
-        <v>46022.00203703704</v>
+        <v>46021.72858796296</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>195</v>
@@ -2044,7 +2040,7 @@
         <v>199</v>
       </c>
       <c r="G28" s="2">
-        <v>20.2</v>
+        <v>30.75</v>
       </c>
       <c r="H28" s="2">
         <v>0</v>
@@ -2061,13 +2057,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>46021.49394675926</v>
+        <v>46021.00030092592</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D29" s="2">
-        <v>46022.00222222223</v>
+        <v>46021.50903935185</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>195</v>
@@ -2076,7 +2072,7 @@
         <v>199</v>
       </c>
       <c r="G29" s="2">
-        <v>20.2</v>
+        <v>19.65</v>
       </c>
       <c r="H29" s="2">
         <v>0</v>
@@ -2093,22 +2089,18 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>46021.32273148148</v>
+        <v>46021.48512731482</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D30" s="2">
-        <v>46021.72858796296</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
         <v>199</v>
       </c>
       <c r="G30" s="2">
-        <v>30.75</v>
+        <v>23</v>
       </c>
       <c r="H30" s="2">
         <v>0</v>
@@ -2125,13 +2117,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>46021.00030092592</v>
+        <v>46021.49179398148</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D31" s="2">
-        <v>46021.50903935185</v>
+        <v>46021.60519675926</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>195</v>
@@ -2140,7 +2132,7 @@
         <v>199</v>
       </c>
       <c r="G31" s="2">
-        <v>19.65</v>
+        <v>20.2</v>
       </c>
       <c r="H31" s="2">
         <v>0</v>
@@ -2157,18 +2149,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>46021.98780092593</v>
+        <v>46021.53125</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+      <c r="D32" s="2">
+        <v>46021.92871527778</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F32" s="2" t="s">
         <v>199</v>
       </c>
       <c r="G32" s="2">
-        <v>23</v>
+        <v>20.2</v>
       </c>
       <c r="H32" s="2">
         <v>0</v>
@@ -2185,22 +2181,18 @@
         <v>32</v>
       </c>
       <c r="B33" s="2">
-        <v>46021.49717592593</v>
+        <v>46021.99130787037</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D33" s="2">
-        <v>46022.01121527778</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
         <v>199</v>
       </c>
       <c r="G33" s="2">
-        <v>22.4</v>
+        <v>20.2</v>
       </c>
       <c r="H33" s="2">
         <v>0</v>
@@ -2217,13 +2209,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <v>46021.49799768518</v>
+        <v>46021.49394675926</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D34" s="2">
-        <v>46022.01118055556</v>
+        <v>46022.00222222223</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>195</v>
@@ -2232,7 +2224,7 @@
         <v>199</v>
       </c>
       <c r="G34" s="2">
-        <v>23</v>
+        <v>20.2</v>
       </c>
       <c r="H34" s="2">
         <v>0</v>
@@ -2249,13 +2241,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="2">
-        <v>46021.00009259259</v>
+        <v>46021.49797453704</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D35" s="2">
-        <v>46021.25017361111</v>
+        <v>46022.00203703704</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>195</v>
@@ -2281,13 +2273,17 @@
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>46021.48512731482</v>
+        <v>46021.49799768518</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
+      <c r="D36" s="2">
+        <v>46022.01118055556</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F36" s="2" t="s">
         <v>199</v>
       </c>
@@ -2309,18 +2305,22 @@
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>46021.99130787037</v>
+        <v>46021.49717592593</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
+      <c r="D37" s="2">
+        <v>46022.01121527778</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F37" s="2" t="s">
         <v>199</v>
       </c>
       <c r="G37" s="2">
-        <v>20.2</v>
+        <v>22.4</v>
       </c>
       <c r="H37" s="2">
         <v>0</v>
@@ -2337,13 +2337,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>46021.53125</v>
+        <v>46021.00009259259</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D38" s="2">
-        <v>46021.92871527778</v>
+        <v>46021.25017361111</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>195</v>
@@ -2401,13 +2401,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>46021.30290509259</v>
+        <v>46021.07305555556</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D40" s="2">
-        <v>46021.7384375</v>
+        <v>46021.40865740741</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>195</v>
@@ -2416,7 +2416,7 @@
         <v>200</v>
       </c>
       <c r="G40" s="2">
-        <v>18.35</v>
+        <v>23</v>
       </c>
       <c r="H40" s="2">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>46021.07305555556</v>
+        <v>46021.30290509259</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D41" s="2">
-        <v>46021.40865740741</v>
+        <v>46021.7384375</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>195</v>
@@ -2448,7 +2448,7 @@
         <v>200</v>
       </c>
       <c r="G41" s="2">
-        <v>23</v>
+        <v>18.35</v>
       </c>
       <c r="H41" s="2">
         <v>0</v>
@@ -2465,22 +2465,18 @@
         <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>46021.07203703704</v>
+        <v>46021.69020833333</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D42" s="2">
-        <v>46021.40556712963</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
       <c r="F42" s="2" t="s">
         <v>201</v>
       </c>
       <c r="G42" s="2">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -2497,22 +2493,18 @@
         <v>42</v>
       </c>
       <c r="B43" s="2">
-        <v>46021.68973379629</v>
+        <v>46021.68931712963</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D43" s="2">
-        <v>46022.05234953704</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
       <c r="F43" s="2" t="s">
         <v>201</v>
       </c>
       <c r="G43" s="2">
-        <v>29.25</v>
+        <v>17</v>
       </c>
       <c r="H43" s="2">
         <v>0</v>
@@ -2529,18 +2521,22 @@
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>46021.68931712963</v>
+        <v>46021.68973379629</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
+      <c r="D44" s="2">
+        <v>46022.05234953704</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F44" s="2" t="s">
         <v>201</v>
       </c>
       <c r="G44" s="2">
-        <v>17</v>
+        <v>29.25</v>
       </c>
       <c r="H44" s="2">
         <v>0</v>
@@ -2557,18 +2553,22 @@
         <v>44</v>
       </c>
       <c r="B45" s="2">
-        <v>46021.69020833333</v>
+        <v>46021.07203703704</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
+      <c r="D45" s="2">
+        <v>46021.40556712963</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F45" s="2" t="s">
         <v>201</v>
       </c>
       <c r="G45" s="2">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>46021.29143518519</v>
+        <v>46021.52267361111</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D47" s="2">
-        <v>46021.71001157408</v>
+        <v>46021.67354166666</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>195</v>
@@ -2632,7 +2632,7 @@
         <v>202</v>
       </c>
       <c r="G47" s="2">
-        <v>40.5</v>
+        <v>35.5</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
@@ -2646,16 +2646,16 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>46021.52267361111</v>
+        <v>46021.29143518519</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D48" s="2">
-        <v>46021.67354166666</v>
+        <v>46021.71001157408</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>195</v>
@@ -2664,7 +2664,7 @@
         <v>202</v>
       </c>
       <c r="G48" s="2">
-        <v>35.5</v>
+        <v>40.5</v>
       </c>
       <c r="H48" s="2">
         <v>0</v>
@@ -2681,13 +2681,13 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>46021.31967592592</v>
+        <v>46021.31978009259</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D49" s="2">
-        <v>46021.74001157407</v>
+        <v>46021.74443287037</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>195</v>
@@ -2713,13 +2713,13 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>46021.31928240741</v>
+        <v>46021.31502314815</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D50" s="2">
-        <v>46021.72253472222</v>
+        <v>46021.74859953704</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>195</v>
@@ -2728,7 +2728,7 @@
         <v>203</v>
       </c>
       <c r="G50" s="2">
-        <v>20.2</v>
+        <v>25</v>
       </c>
       <c r="H50" s="2">
         <v>0</v>
@@ -2745,13 +2745,13 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>46021.31283564815</v>
+        <v>46021.31964120371</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D51" s="2">
-        <v>46021.71603009259</v>
+        <v>46021.73979166667</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>195</v>
@@ -2760,7 +2760,7 @@
         <v>203</v>
       </c>
       <c r="G51" s="2">
-        <v>18.75</v>
+        <v>23.85</v>
       </c>
       <c r="H51" s="2">
         <v>0</v>
@@ -2777,13 +2777,13 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>46021.31336805555</v>
+        <v>46021.3171412037</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D52" s="2">
-        <v>46021.71479166667</v>
+        <v>46021.75480324074</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>195</v>
@@ -2792,7 +2792,7 @@
         <v>203</v>
       </c>
       <c r="G52" s="2">
-        <v>19.6</v>
+        <v>24.45</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -2809,13 +2809,13 @@
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>46021.31964120371</v>
+        <v>46021.31821759259</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D53" s="2">
-        <v>46021.73979166667</v>
+        <v>46021.7362037037</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>195</v>
@@ -2824,7 +2824,7 @@
         <v>203</v>
       </c>
       <c r="G53" s="2">
-        <v>23.85</v>
+        <v>19.25</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
@@ -2841,13 +2841,13 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>46021.3171412037</v>
+        <v>46021.3334375</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D54" s="2">
-        <v>46021.75480324074</v>
+        <v>46021.75822916667</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>195</v>
@@ -2856,7 +2856,7 @@
         <v>203</v>
       </c>
       <c r="G54" s="2">
-        <v>24.45</v>
+        <v>20.95</v>
       </c>
       <c r="H54" s="2">
         <v>0</v>
@@ -2873,13 +2873,13 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>46021.31502314815</v>
+        <v>46021.31283564815</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D55" s="2">
-        <v>46021.74859953704</v>
+        <v>46021.71603009259</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>195</v>
@@ -2888,7 +2888,7 @@
         <v>203</v>
       </c>
       <c r="G55" s="2">
-        <v>25</v>
+        <v>18.75</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -2905,13 +2905,13 @@
         <v>54</v>
       </c>
       <c r="B56" s="2">
-        <v>46021.31793981481</v>
+        <v>46021.31336805555</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D56" s="2">
-        <v>46021.74293981482</v>
+        <v>46021.71479166667</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>195</v>
@@ -2920,7 +2920,7 @@
         <v>203</v>
       </c>
       <c r="G56" s="2">
-        <v>23</v>
+        <v>19.6</v>
       </c>
       <c r="H56" s="2">
         <v>0</v>
@@ -2937,13 +2937,13 @@
         <v>55</v>
       </c>
       <c r="B57" s="2">
-        <v>46021.32982638889</v>
+        <v>46021.31928240741</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D57" s="2">
-        <v>46021.70662037037</v>
+        <v>46021.72253472222</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>195</v>
@@ -2952,7 +2952,7 @@
         <v>203</v>
       </c>
       <c r="G57" s="2">
-        <v>22.4</v>
+        <v>20.2</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -2969,13 +2969,13 @@
         <v>56</v>
       </c>
       <c r="B58" s="2">
-        <v>46021.31821759259</v>
+        <v>46021.41666666666</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D58" s="2">
-        <v>46021.7362037037</v>
+        <v>46021.68337962963</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>195</v>
@@ -2984,7 +2984,7 @@
         <v>203</v>
       </c>
       <c r="G58" s="2">
-        <v>19.25</v>
+        <v>24.8</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -3001,13 +3001,13 @@
         <v>57</v>
       </c>
       <c r="B59" s="2">
-        <v>46021.31978009259</v>
+        <v>46021.31385416666</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D59" s="2">
-        <v>46021.74443287037</v>
+        <v>46021.72300925926</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>195</v>
@@ -3016,7 +3016,7 @@
         <v>203</v>
       </c>
       <c r="G59" s="2">
-        <v>23.35</v>
+        <v>22.4</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -3033,25 +3033,25 @@
         <v>58</v>
       </c>
       <c r="B60" s="2">
-        <v>46021.5</v>
+        <v>46021.32166666666</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D60" s="2">
-        <v>46021.5</v>
+        <v>46021.75599537037</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>203</v>
       </c>
       <c r="G60" s="2">
-        <v>23.35</v>
+        <v>19.6</v>
       </c>
       <c r="H60" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I60" s="2">
         <v>0</v>
@@ -3065,13 +3065,13 @@
         <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>46021.3334375</v>
+        <v>46021.32228009259</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D61" s="2">
-        <v>46021.75822916667</v>
+        <v>46021.73648148148</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>195</v>
@@ -3097,13 +3097,13 @@
         <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>46021.41666666666</v>
+        <v>46021.31793981481</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D62" s="2">
-        <v>46021.68337962963</v>
+        <v>46021.74293981482</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>195</v>
@@ -3112,7 +3112,7 @@
         <v>203</v>
       </c>
       <c r="G62" s="2">
-        <v>24.8</v>
+        <v>23</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>
@@ -3129,13 +3129,13 @@
         <v>61</v>
       </c>
       <c r="B63" s="2">
-        <v>46021.31385416666</v>
+        <v>46021.32982638889</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D63" s="2">
-        <v>46021.72300925926</v>
+        <v>46021.70662037037</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>195</v>
@@ -3161,25 +3161,25 @@
         <v>62</v>
       </c>
       <c r="B64" s="2">
-        <v>46021.32166666666</v>
+        <v>46021.5</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D64" s="2">
-        <v>46021.75599537037</v>
+        <v>46021.5</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>203</v>
       </c>
       <c r="G64" s="2">
-        <v>19.6</v>
+        <v>23.35</v>
       </c>
       <c r="H64" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I64" s="2">
         <v>0</v>
@@ -3193,13 +3193,13 @@
         <v>63</v>
       </c>
       <c r="B65" s="2">
-        <v>46021.32228009259</v>
+        <v>46021.31967592592</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D65" s="2">
-        <v>46021.73648148148</v>
+        <v>46021.74001157407</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>195</v>
@@ -3208,7 +3208,7 @@
         <v>203</v>
       </c>
       <c r="G65" s="2">
-        <v>20.95</v>
+        <v>23.35</v>
       </c>
       <c r="H65" s="2">
         <v>0</v>
@@ -3225,13 +3225,13 @@
         <v>64</v>
       </c>
       <c r="B66" s="2">
-        <v>46021.30341435185</v>
+        <v>46021.30033564815</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D66" s="2">
-        <v>46021.6937962963</v>
+        <v>46021.49231481482</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>195</v>
@@ -3240,7 +3240,7 @@
         <v>204</v>
       </c>
       <c r="G66" s="2">
-        <v>19.6</v>
+        <v>19.25</v>
       </c>
       <c r="H66" s="2">
         <v>0</v>
@@ -3257,13 +3257,13 @@
         <v>65</v>
       </c>
       <c r="B67" s="2">
-        <v>46021.40486111111</v>
+        <v>46021.30284722222</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D67" s="2">
-        <v>46021.66666666666</v>
+        <v>46021.53158564815</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>195</v>
@@ -3272,7 +3272,7 @@
         <v>204</v>
       </c>
       <c r="G67" s="2">
-        <v>19.75</v>
+        <v>19.25</v>
       </c>
       <c r="H67" s="2">
         <v>0</v>
@@ -3289,13 +3289,13 @@
         <v>66</v>
       </c>
       <c r="B68" s="2">
-        <v>46021.29760416667</v>
+        <v>46021.30393518518</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D68" s="2">
-        <v>46021.66974537037</v>
+        <v>46021.61788194445</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>195</v>
@@ -3304,7 +3304,7 @@
         <v>204</v>
       </c>
       <c r="G68" s="2">
-        <v>19.75</v>
+        <v>19.35</v>
       </c>
       <c r="H68" s="2">
         <v>0</v>
@@ -3321,13 +3321,13 @@
         <v>67</v>
       </c>
       <c r="B69" s="2">
-        <v>46021.30704861111</v>
+        <v>46021.29755787037</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D69" s="2">
-        <v>46021.66810185185</v>
+        <v>46021.61045138889</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>195</v>
@@ -3336,7 +3336,7 @@
         <v>204</v>
       </c>
       <c r="G69" s="2">
-        <v>19.25</v>
+        <v>19.6</v>
       </c>
       <c r="H69" s="2">
         <v>0</v>
@@ -3353,18 +3353,22 @@
         <v>68</v>
       </c>
       <c r="B70" s="2">
-        <v>46021.3071412037</v>
+        <v>46021.30704861111</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
+      <c r="D70" s="2">
+        <v>46021.66810185185</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F70" s="2" t="s">
         <v>204</v>
       </c>
       <c r="G70" s="2">
-        <v>18.75</v>
+        <v>19.25</v>
       </c>
       <c r="H70" s="2">
         <v>0</v>
@@ -3381,22 +3385,18 @@
         <v>69</v>
       </c>
       <c r="B71" s="2">
-        <v>46021.30033564815</v>
+        <v>46021.3071412037</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D71" s="2">
-        <v>46021.49231481482</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
       <c r="F71" s="2" t="s">
         <v>204</v>
       </c>
       <c r="G71" s="2">
-        <v>19.25</v>
+        <v>18.75</v>
       </c>
       <c r="H71" s="2">
         <v>0</v>
@@ -3413,13 +3413,13 @@
         <v>70</v>
       </c>
       <c r="B72" s="2">
-        <v>46021.30284722222</v>
+        <v>46021.30064814815</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D72" s="2">
-        <v>46021.53158564815</v>
+        <v>46021.66930555556</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>195</v>
@@ -3428,7 +3428,7 @@
         <v>204</v>
       </c>
       <c r="G72" s="2">
-        <v>19.25</v>
+        <v>19.6</v>
       </c>
       <c r="H72" s="2">
         <v>0</v>
@@ -3445,13 +3445,13 @@
         <v>71</v>
       </c>
       <c r="B73" s="2">
-        <v>46021.33170138889</v>
+        <v>46021.40924768519</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D73" s="2">
-        <v>46021.56640046297</v>
+        <v>46021.62113425926</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>195</v>
@@ -3460,7 +3460,7 @@
         <v>204</v>
       </c>
       <c r="G73" s="2">
-        <v>19.6</v>
+        <v>19.25</v>
       </c>
       <c r="H73" s="2">
         <v>0</v>
@@ -3477,13 +3477,13 @@
         <v>72</v>
       </c>
       <c r="B74" s="2">
-        <v>46021.30393518518</v>
+        <v>46021.33170138889</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D74" s="2">
-        <v>46021.61788194445</v>
+        <v>46021.56640046297</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>195</v>
@@ -3492,7 +3492,7 @@
         <v>204</v>
       </c>
       <c r="G74" s="2">
-        <v>19.35</v>
+        <v>19.6</v>
       </c>
       <c r="H74" s="2">
         <v>0</v>
@@ -3509,13 +3509,13 @@
         <v>73</v>
       </c>
       <c r="B75" s="2">
-        <v>46021.30064814815</v>
+        <v>46021.29760416667</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D75" s="2">
-        <v>46021.66930555556</v>
+        <v>46021.66974537037</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>195</v>
@@ -3524,7 +3524,7 @@
         <v>204</v>
       </c>
       <c r="G75" s="2">
-        <v>19.6</v>
+        <v>19.75</v>
       </c>
       <c r="H75" s="2">
         <v>0</v>
@@ -3541,13 +3541,13 @@
         <v>74</v>
       </c>
       <c r="B76" s="2">
-        <v>46021.34483796296</v>
+        <v>46021.30302083334</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D76" s="2">
-        <v>46021.52200231481</v>
+        <v>46021.74266203704</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>195</v>
@@ -3556,7 +3556,7 @@
         <v>204</v>
       </c>
       <c r="G76" s="2">
-        <v>18.6</v>
+        <v>22.4</v>
       </c>
       <c r="H76" s="2">
         <v>0</v>
@@ -3573,13 +3573,13 @@
         <v>75</v>
       </c>
       <c r="B77" s="2">
-        <v>46021.29464120371</v>
+        <v>46021.29497685185</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D77" s="2">
-        <v>46021.70753472222</v>
+        <v>46021.52920138889</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>195</v>
@@ -3588,7 +3588,7 @@
         <v>204</v>
       </c>
       <c r="G77" s="2">
-        <v>22.75</v>
+        <v>19.25</v>
       </c>
       <c r="H77" s="2">
         <v>0</v>
@@ -3605,13 +3605,13 @@
         <v>76</v>
       </c>
       <c r="B78" s="2">
-        <v>46021.29497685185</v>
+        <v>46021.30341435185</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D78" s="2">
-        <v>46021.52920138889</v>
+        <v>46021.6937962963</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>195</v>
@@ -3620,7 +3620,7 @@
         <v>204</v>
       </c>
       <c r="G78" s="2">
-        <v>19.25</v>
+        <v>19.6</v>
       </c>
       <c r="H78" s="2">
         <v>0</v>
@@ -3637,13 +3637,13 @@
         <v>77</v>
       </c>
       <c r="B79" s="2">
-        <v>46021.40924768519</v>
+        <v>46021.29464120371</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D79" s="2">
-        <v>46021.62113425926</v>
+        <v>46021.70753472222</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>195</v>
@@ -3652,7 +3652,7 @@
         <v>204</v>
       </c>
       <c r="G79" s="2">
-        <v>19.25</v>
+        <v>22.75</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
@@ -3669,13 +3669,13 @@
         <v>78</v>
       </c>
       <c r="B80" s="2">
-        <v>46021.30302083334</v>
+        <v>46021.34483796296</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D80" s="2">
-        <v>46021.74266203704</v>
+        <v>46021.52200231481</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>195</v>
@@ -3684,7 +3684,7 @@
         <v>204</v>
       </c>
       <c r="G80" s="2">
-        <v>22.4</v>
+        <v>18.6</v>
       </c>
       <c r="H80" s="2">
         <v>0</v>
@@ -3701,13 +3701,13 @@
         <v>79</v>
       </c>
       <c r="B81" s="2">
-        <v>46021.29755787037</v>
+        <v>46021.40486111111</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D81" s="2">
-        <v>46021.61045138889</v>
+        <v>46021.66666666666</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>195</v>
@@ -3716,7 +3716,7 @@
         <v>204</v>
       </c>
       <c r="G81" s="2">
-        <v>19.6</v>
+        <v>19.75</v>
       </c>
       <c r="H81" s="2">
         <v>0</v>
@@ -3733,13 +3733,13 @@
         <v>80</v>
       </c>
       <c r="B82" s="2">
-        <v>46021.32637731481</v>
+        <v>46021.51936342593</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D82" s="2">
-        <v>46021.69166666667</v>
+        <v>46021.5194675926</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>195</v>
@@ -3748,7 +3748,7 @@
         <v>205</v>
       </c>
       <c r="G82" s="2">
-        <v>23</v>
+        <v>19.6</v>
       </c>
       <c r="H82" s="2">
         <v>0</v>
@@ -3765,13 +3765,13 @@
         <v>81</v>
       </c>
       <c r="B83" s="2">
-        <v>46021.51936342593</v>
+        <v>46021.32626157408</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D83" s="2">
-        <v>46021.5194675926</v>
+        <v>46021.69688657407</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>195</v>
@@ -3780,7 +3780,7 @@
         <v>205</v>
       </c>
       <c r="G83" s="2">
-        <v>19.6</v>
+        <v>23.35</v>
       </c>
       <c r="H83" s="2">
         <v>0</v>
@@ -3797,13 +3797,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="2">
-        <v>46021.32704861111</v>
+        <v>46021.32637731481</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D84" s="2">
-        <v>46021.57854166667</v>
+        <v>46021.69166666667</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>195</v>
@@ -3812,7 +3812,7 @@
         <v>205</v>
       </c>
       <c r="G84" s="2">
-        <v>23.35</v>
+        <v>23</v>
       </c>
       <c r="H84" s="2">
         <v>0</v>
@@ -3829,13 +3829,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="2">
-        <v>46021.32626157408</v>
+        <v>46021.32704861111</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D85" s="2">
-        <v>46021.69688657407</v>
+        <v>46021.57854166667</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>195</v>
@@ -3861,13 +3861,13 @@
         <v>84</v>
       </c>
       <c r="B86" s="2">
-        <v>46021.31924768518</v>
+        <v>46021.57987268519</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D86" s="2">
-        <v>46021.50954861111</v>
+        <v>46021.71850694445</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>195</v>
@@ -3893,13 +3893,13 @@
         <v>85</v>
       </c>
       <c r="B87" s="2">
-        <v>46021.5975</v>
+        <v>46021.30517361111</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D87" s="2">
-        <v>46021.71859953704</v>
+        <v>46021.56539351852</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>195</v>
@@ -3908,7 +3908,7 @@
         <v>206</v>
       </c>
       <c r="G87" s="2">
-        <v>18.6</v>
+        <v>17.85</v>
       </c>
       <c r="H87" s="2">
         <v>0</v>
@@ -3922,16 +3922,16 @@
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B88" s="2">
-        <v>46021.30851851852</v>
+        <v>46021.52431712963</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D88" s="2">
-        <v>46021.5903587963</v>
+        <v>46021.71839120371</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>195</v>
@@ -3940,7 +3940,7 @@
         <v>206</v>
       </c>
       <c r="G88" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H88" s="2">
         <v>0</v>
@@ -3954,16 +3954,16 @@
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B89" s="2">
-        <v>46021.3017824074</v>
+        <v>46021.30329861111</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D89" s="2">
-        <v>46021.56452546296</v>
+        <v>46021.53689814815</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>195</v>
@@ -3972,7 +3972,7 @@
         <v>206</v>
       </c>
       <c r="G89" s="2">
-        <v>19.25</v>
+        <v>18.35</v>
       </c>
       <c r="H89" s="2">
         <v>0</v>
@@ -3986,16 +3986,16 @@
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B90" s="2">
-        <v>46021.30694444444</v>
+        <v>46021.58563657408</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D90" s="2">
-        <v>46021.55842592593</v>
+        <v>46021.71880787037</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>195</v>
@@ -4018,16 +4018,16 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B91" s="2">
-        <v>46021.71859953704</v>
+        <v>46021.546875</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D91" s="2">
-        <v>46021.71865740741</v>
+        <v>46021.72003472222</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>195</v>
@@ -4036,7 +4036,7 @@
         <v>206</v>
       </c>
       <c r="G91" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H91" s="2">
         <v>0</v>
@@ -4050,16 +4050,16 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B92" s="2">
-        <v>46021.57987268519</v>
+        <v>46021.3017824074</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D92" s="2">
-        <v>46021.71850694445</v>
+        <v>46021.56452546296</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>195</v>
@@ -4068,7 +4068,7 @@
         <v>206</v>
       </c>
       <c r="G92" s="2">
-        <v>19.75</v>
+        <v>19.25</v>
       </c>
       <c r="H92" s="2">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B93" s="2">
         <v>46021.57658564814</v>
@@ -4117,13 +4117,13 @@
         <v>88</v>
       </c>
       <c r="B94" s="2">
-        <v>46021.30880787037</v>
+        <v>46021.30148148148</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D94" s="2">
-        <v>46021.53739583334</v>
+        <v>46021.57016203704</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>195</v>
@@ -4146,16 +4146,16 @@
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B95" s="2">
-        <v>46021.30381944445</v>
+        <v>46021.31924768518</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D95" s="2">
-        <v>46021.59515046296</v>
+        <v>46021.50954861111</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>195</v>
@@ -4164,7 +4164,7 @@
         <v>206</v>
       </c>
       <c r="G95" s="2">
-        <v>18.35</v>
+        <v>19.75</v>
       </c>
       <c r="H95" s="2">
         <v>0</v>
@@ -4178,16 +4178,16 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B96" s="2">
-        <v>46021.30329861111</v>
+        <v>46021.5975</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D96" s="2">
-        <v>46021.53689814815</v>
+        <v>46021.71859953704</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>195</v>
@@ -4196,7 +4196,7 @@
         <v>206</v>
       </c>
       <c r="G96" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H96" s="2">
         <v>0</v>
@@ -4210,16 +4210,16 @@
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B97" s="2">
-        <v>46021.55568287037</v>
+        <v>46021.30344907408</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D97" s="2">
-        <v>46021.71855324074</v>
+        <v>46021.71900462963</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>195</v>
@@ -4242,16 +4242,16 @@
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B98" s="2">
-        <v>46021.30148148148</v>
+        <v>46021.29760416667</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D98" s="2">
-        <v>46021.57016203704</v>
+        <v>46021.59293981481</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>195</v>
@@ -4260,7 +4260,7 @@
         <v>206</v>
       </c>
       <c r="G98" s="2">
-        <v>18.6</v>
+        <v>19.25</v>
       </c>
       <c r="H98" s="2">
         <v>0</v>
@@ -4274,16 +4274,16 @@
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B99" s="2">
-        <v>46021.58563657408</v>
+        <v>46021.55568287037</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D99" s="2">
-        <v>46021.71880787037</v>
+        <v>46021.71855324074</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>195</v>
@@ -4292,7 +4292,7 @@
         <v>206</v>
       </c>
       <c r="G99" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H99" s="2">
         <v>0</v>
@@ -4306,16 +4306,16 @@
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B100" s="2">
-        <v>46021.30387731481</v>
+        <v>46021.30880787037</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D100" s="2">
-        <v>46021.53256944445</v>
+        <v>46021.53739583334</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>195</v>
@@ -4324,7 +4324,7 @@
         <v>206</v>
       </c>
       <c r="G100" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H100" s="2">
         <v>0</v>
@@ -4338,16 +4338,16 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B101" s="2">
-        <v>46021.546875</v>
+        <v>46021.60690972222</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D101" s="2">
-        <v>46021.72003472222</v>
+        <v>46021.71853009259</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>195</v>
@@ -4356,7 +4356,7 @@
         <v>206</v>
       </c>
       <c r="G101" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H101" s="2">
         <v>0</v>
@@ -4370,16 +4370,16 @@
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B102" s="2">
-        <v>46021.30517361111</v>
+        <v>46021.30405092592</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D102" s="2">
-        <v>46021.56539351852</v>
+        <v>46021.50297453703</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>195</v>
@@ -4388,7 +4388,7 @@
         <v>206</v>
       </c>
       <c r="G102" s="2">
-        <v>17.85</v>
+        <v>19.6</v>
       </c>
       <c r="H102" s="2">
         <v>0</v>
@@ -4402,16 +4402,16 @@
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B103" s="2">
-        <v>46021.58520833333</v>
+        <v>46021.52453703704</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D103" s="2">
-        <v>46021.71974537037</v>
+        <v>46021.71837962963</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>195</v>
@@ -4420,7 +4420,7 @@
         <v>206</v>
       </c>
       <c r="G103" s="2">
-        <v>17.85</v>
+        <v>19.6</v>
       </c>
       <c r="H103" s="2">
         <v>0</v>
@@ -4434,16 +4434,16 @@
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B104" s="2">
-        <v>46021.30069444444</v>
+        <v>46021.30255787037</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D104" s="2">
-        <v>46021.51075231482</v>
+        <v>46021.54674768518</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>195</v>
@@ -4466,16 +4466,16 @@
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B105" s="2">
-        <v>46021.52431712963</v>
+        <v>46021.5621875</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D105" s="2">
-        <v>46021.71839120371</v>
+        <v>46021.71854166667</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>195</v>
@@ -4498,16 +4498,16 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B106" s="2">
-        <v>46021.30166666667</v>
+        <v>46021.30387731481</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D106" s="2">
-        <v>46021.71854166667</v>
+        <v>46021.53256944445</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>195</v>
@@ -4516,7 +4516,7 @@
         <v>206</v>
       </c>
       <c r="G106" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H106" s="2">
         <v>0</v>
@@ -4530,16 +4530,16 @@
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B107" s="2">
-        <v>46021.30173611111</v>
+        <v>46021.30851851852</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D107" s="2">
-        <v>46021.71909722222</v>
+        <v>46021.5903587963</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>195</v>
@@ -4548,7 +4548,7 @@
         <v>206</v>
       </c>
       <c r="G107" s="2">
-        <v>22.4</v>
+        <v>18.6</v>
       </c>
       <c r="H107" s="2">
         <v>0</v>
@@ -4562,16 +4562,16 @@
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B108" s="2">
-        <v>46021.60690972222</v>
+        <v>46021.58520833333</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D108" s="2">
-        <v>46021.71853009259</v>
+        <v>46021.71974537037</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>195</v>
@@ -4580,7 +4580,7 @@
         <v>206</v>
       </c>
       <c r="G108" s="2">
-        <v>18.6</v>
+        <v>17.85</v>
       </c>
       <c r="H108" s="2">
         <v>0</v>
@@ -4594,16 +4594,16 @@
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B109" s="2">
-        <v>46021.5621875</v>
+        <v>46021.30069444444</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D109" s="2">
-        <v>46021.71854166667</v>
+        <v>46021.51075231482</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>195</v>
@@ -4626,16 +4626,16 @@
     </row>
     <row r="110" spans="1:10">
       <c r="A110" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B110" s="2">
-        <v>46021.52453703704</v>
+        <v>46021.30381944445</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D110" s="2">
-        <v>46021.71837962963</v>
+        <v>46021.59515046296</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>195</v>
@@ -4644,7 +4644,7 @@
         <v>206</v>
       </c>
       <c r="G110" s="2">
-        <v>19.6</v>
+        <v>18.35</v>
       </c>
       <c r="H110" s="2">
         <v>0</v>
@@ -4661,13 +4661,13 @@
         <v>98</v>
       </c>
       <c r="B111" s="2">
-        <v>46021.30405092592</v>
+        <v>46021.30173611111</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D111" s="2">
-        <v>46021.50297453703</v>
+        <v>46021.71909722222</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>195</v>
@@ -4676,7 +4676,7 @@
         <v>206</v>
       </c>
       <c r="G111" s="2">
-        <v>19.6</v>
+        <v>22.4</v>
       </c>
       <c r="H111" s="2">
         <v>0</v>
@@ -4693,13 +4693,13 @@
         <v>99</v>
       </c>
       <c r="B112" s="2">
-        <v>46021.29760416667</v>
+        <v>46021.71859953704</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D112" s="2">
-        <v>46021.59293981481</v>
+        <v>46021.71865740741</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>195</v>
@@ -4708,7 +4708,7 @@
         <v>206</v>
       </c>
       <c r="G112" s="2">
-        <v>19.25</v>
+        <v>18.6</v>
       </c>
       <c r="H112" s="2">
         <v>0</v>
@@ -4722,16 +4722,16 @@
     </row>
     <row r="113" spans="1:10">
       <c r="A113" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B113" s="2">
-        <v>46021.30344907408</v>
+        <v>46021.30694444444</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D113" s="2">
-        <v>46021.71900462963</v>
+        <v>46021.55842592593</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>195</v>
@@ -4740,7 +4740,7 @@
         <v>206</v>
       </c>
       <c r="G113" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H113" s="2">
         <v>0</v>
@@ -4754,16 +4754,16 @@
     </row>
     <row r="114" spans="1:10">
       <c r="A114" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B114" s="2">
-        <v>46021.30255787037</v>
+        <v>46021.30166666667</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D114" s="2">
-        <v>46021.54674768518</v>
+        <v>46021.71854166667</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>195</v>
@@ -4772,7 +4772,7 @@
         <v>206</v>
       </c>
       <c r="G114" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H114" s="2">
         <v>0</v>
@@ -4885,13 +4885,13 @@
         <v>104</v>
       </c>
       <c r="B118" s="2">
-        <v>46021.31453703704</v>
+        <v>46021.37400462963</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D118" s="2">
-        <v>46021.70487268519</v>
+        <v>46021.73636574074</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>195</v>
@@ -4900,7 +4900,7 @@
         <v>209</v>
       </c>
       <c r="G118" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H118" s="2">
         <v>0</v>
@@ -4917,13 +4917,13 @@
         <v>105</v>
       </c>
       <c r="B119" s="2">
-        <v>46021.31305555555</v>
+        <v>46021.31333333333</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D119" s="2">
-        <v>46021.56645833333</v>
+        <v>46021.70833333334</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>195</v>
@@ -4932,7 +4932,7 @@
         <v>209</v>
       </c>
       <c r="G119" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H119" s="2">
         <v>0</v>
@@ -4949,13 +4949,13 @@
         <v>106</v>
       </c>
       <c r="B120" s="2">
-        <v>46021.31333333333</v>
+        <v>46021.31453703704</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D120" s="2">
-        <v>46021.70833333334</v>
+        <v>46021.70487268519</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>195</v>
@@ -5013,13 +5013,13 @@
         <v>107</v>
       </c>
       <c r="B122" s="2">
-        <v>46021.37400462963</v>
+        <v>46021.31305555555</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D122" s="2">
-        <v>46021.73636574074</v>
+        <v>46021.56645833333</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>195</v>
@@ -5077,13 +5077,13 @@
         <v>109</v>
       </c>
       <c r="B124" s="2">
-        <v>46021.37207175926</v>
+        <v>46021.24775462963</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D124" s="2">
-        <v>46021.62596064815</v>
+        <v>46021.70616898148</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>195</v>
@@ -5092,7 +5092,7 @@
         <v>211</v>
       </c>
       <c r="G124" s="2">
-        <v>18.35</v>
+        <v>22.4</v>
       </c>
       <c r="H124" s="2">
         <v>0</v>
@@ -5109,13 +5109,13 @@
         <v>110</v>
       </c>
       <c r="B125" s="2">
-        <v>46021.37578703704</v>
+        <v>46021.37207175926</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D125" s="2">
-        <v>46021.68872685185</v>
+        <v>46021.62596064815</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>195</v>
@@ -5124,7 +5124,7 @@
         <v>211</v>
       </c>
       <c r="G125" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H125" s="2">
         <v>0</v>
@@ -5141,25 +5141,25 @@
         <v>111</v>
       </c>
       <c r="B126" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.31255787037</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D126" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.62383101852</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>211</v>
       </c>
       <c r="G126" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H126" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I126" s="2">
         <v>0</v>
@@ -5173,25 +5173,25 @@
         <v>112</v>
       </c>
       <c r="B127" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.37517361111</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D127" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.73476851852</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>211</v>
       </c>
       <c r="G127" s="2">
-        <v>18.35</v>
+        <v>15.9</v>
       </c>
       <c r="H127" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I127" s="2">
         <v>0</v>
@@ -5202,31 +5202,31 @@
     </row>
     <row r="128" spans="1:10">
       <c r="A128" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B128" s="2">
-        <v>46021.24775462963</v>
+        <v>46021</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D128" s="2">
-        <v>46021.70616898148</v>
+        <v>46021</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>211</v>
       </c>
       <c r="G128" s="2">
-        <v>22.4</v>
+        <v>15.9</v>
       </c>
       <c r="H128" s="2">
         <v>0</v>
       </c>
       <c r="I128" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>244</v>
@@ -5234,16 +5234,16 @@
     </row>
     <row r="129" spans="1:10">
       <c r="A129" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B129" s="2">
-        <v>46021.36543981481</v>
+        <v>46021.37578703704</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D129" s="2">
-        <v>46021.74340277778</v>
+        <v>46021.68872685185</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>195</v>
@@ -5252,7 +5252,7 @@
         <v>211</v>
       </c>
       <c r="G129" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H129" s="2">
         <v>0</v>
@@ -5266,16 +5266,16 @@
     </row>
     <row r="130" spans="1:10">
       <c r="A130" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B130" s="2">
-        <v>46021.31255787037</v>
+        <v>46021.36637731481</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D130" s="2">
-        <v>46021.62383101852</v>
+        <v>46021.68155092592</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>195</v>
@@ -5284,7 +5284,7 @@
         <v>211</v>
       </c>
       <c r="G130" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H130" s="2">
         <v>0</v>
@@ -5298,16 +5298,16 @@
     </row>
     <row r="131" spans="1:10">
       <c r="A131" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B131" s="2">
-        <v>46021.37517361111</v>
+        <v>46021.36543981481</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D131" s="2">
-        <v>46021.73476851852</v>
+        <v>46021.74340277778</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>195</v>
@@ -5316,7 +5316,7 @@
         <v>211</v>
       </c>
       <c r="G131" s="2">
-        <v>15.9</v>
+        <v>18.35</v>
       </c>
       <c r="H131" s="2">
         <v>0</v>
@@ -5330,19 +5330,19 @@
     </row>
     <row r="132" spans="1:10">
       <c r="A132" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B132" s="2">
-        <v>46021.36637731481</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D132" s="2">
-        <v>46021.68155092592</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>211</v>
@@ -5351,7 +5351,7 @@
         <v>18.35</v>
       </c>
       <c r="H132" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I132" s="2">
         <v>0</v>
@@ -5362,7 +5362,7 @@
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B133" s="2">
         <v>46021.38815972222</v>
@@ -5394,7 +5394,7 @@
     </row>
     <row r="134" spans="1:10">
       <c r="A134" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B134" s="2">
         <v>46021.33333333334</v>
@@ -5426,16 +5426,16 @@
     </row>
     <row r="135" spans="1:10">
       <c r="A135" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B135" s="2">
-        <v>46021</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>192</v>
       </c>
       <c r="D135" s="2">
-        <v>46021</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>192</v>
@@ -5444,13 +5444,13 @@
         <v>211</v>
       </c>
       <c r="G135" s="2">
-        <v>15.9</v>
+        <v>18.35</v>
       </c>
       <c r="H135" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I135" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>244</v>
@@ -5461,25 +5461,25 @@
         <v>120</v>
       </c>
       <c r="B136" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.30929398148</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D136" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.60993055555</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>212</v>
       </c>
       <c r="G136" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H136" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I136" s="2">
         <v>0</v>
@@ -5493,16 +5493,16 @@
         <v>121</v>
       </c>
       <c r="B137" s="2">
-        <v>46021.45833333334</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D137" s="2">
-        <v>46021.6980787037</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>212</v>
@@ -5511,7 +5511,7 @@
         <v>18.35</v>
       </c>
       <c r="H137" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I137" s="2">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         <v>122</v>
       </c>
       <c r="B138" s="2">
-        <v>46021.26021990741</v>
+        <v>46021.29113425926</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D138" s="2">
-        <v>46021.70833333334</v>
+        <v>46021.61934027778</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>195</v>
@@ -5540,7 +5540,7 @@
         <v>212</v>
       </c>
       <c r="G138" s="2">
-        <v>19.65</v>
+        <v>18.35</v>
       </c>
       <c r="H138" s="2">
         <v>0</v>
@@ -5557,13 +5557,13 @@
         <v>123</v>
       </c>
       <c r="B139" s="2">
-        <v>46021.30929398148</v>
+        <v>46021.45498842592</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D139" s="2">
-        <v>46021.60993055555</v>
+        <v>46021.69689814815</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>195</v>
@@ -5572,7 +5572,7 @@
         <v>212</v>
       </c>
       <c r="G139" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H139" s="2">
         <v>0</v>
@@ -5589,13 +5589,13 @@
         <v>124</v>
       </c>
       <c r="B140" s="2">
-        <v>46021.29113425926</v>
+        <v>46021.33418981481</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D140" s="2">
-        <v>46021.61934027778</v>
+        <v>46021.7685300926</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>195</v>
@@ -5653,16 +5653,16 @@
         <v>126</v>
       </c>
       <c r="B142" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.45045138889</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D142" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.70125</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>212</v>
@@ -5671,7 +5671,7 @@
         <v>18.35</v>
       </c>
       <c r="H142" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I142" s="2">
         <v>0</v>
@@ -5685,13 +5685,13 @@
         <v>127</v>
       </c>
       <c r="B143" s="2">
-        <v>46021.2583912037</v>
+        <v>46021.33628472222</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D143" s="2">
-        <v>46021.69268518518</v>
+        <v>46021.4570949074</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>195</v>
@@ -5717,16 +5717,16 @@
         <v>128</v>
       </c>
       <c r="B144" s="2">
-        <v>46021.37467592592</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D144" s="2">
-        <v>46021.69726851852</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>212</v>
@@ -5735,7 +5735,7 @@
         <v>18.35</v>
       </c>
       <c r="H144" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I144" s="2">
         <v>0</v>
@@ -5749,13 +5749,13 @@
         <v>129</v>
       </c>
       <c r="B145" s="2">
-        <v>46021.33418981481</v>
+        <v>46021.30840277778</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D145" s="2">
-        <v>46021.7685300926</v>
+        <v>46021.62440972222</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>195</v>
@@ -5781,25 +5781,25 @@
         <v>130</v>
       </c>
       <c r="B146" s="2">
-        <v>46021.29318287037</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D146" s="2">
-        <v>46021.72958333333</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>212</v>
       </c>
       <c r="G146" s="2">
-        <v>21.8</v>
+        <v>18.35</v>
       </c>
       <c r="H146" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I146" s="2">
         <v>0</v>
@@ -5813,13 +5813,13 @@
         <v>131</v>
       </c>
       <c r="B147" s="2">
-        <v>46021.45960648148</v>
+        <v>46021.26021990741</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D147" s="2">
-        <v>46021.69760416666</v>
+        <v>46021.70833333334</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>195</v>
@@ -5828,7 +5828,7 @@
         <v>212</v>
       </c>
       <c r="G147" s="2">
-        <v>18.35</v>
+        <v>19.65</v>
       </c>
       <c r="H147" s="2">
         <v>0</v>
@@ -5845,13 +5845,13 @@
         <v>132</v>
       </c>
       <c r="B148" s="2">
-        <v>46021.32020833333</v>
+        <v>46021.45833333334</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D148" s="2">
-        <v>46021.62804398148</v>
+        <v>46021.6980787037</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>195</v>
@@ -5877,16 +5877,16 @@
         <v>133</v>
       </c>
       <c r="B149" s="2">
-        <v>46021.45045138889</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D149" s="2">
-        <v>46021.70125</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>212</v>
@@ -5895,7 +5895,7 @@
         <v>18.35</v>
       </c>
       <c r="H149" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I149" s="2">
         <v>0</v>
@@ -5938,19 +5938,19 @@
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B151" s="2">
-        <v>46021.25751157408</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D151" s="2">
-        <v>46021.6255787037</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>212</v>
@@ -5959,7 +5959,7 @@
         <v>18.35</v>
       </c>
       <c r="H151" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I151" s="2">
         <v>0</v>
@@ -5970,16 +5970,16 @@
     </row>
     <row r="152" spans="1:10">
       <c r="A152" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B152" s="2">
-        <v>46021.5277662037</v>
+        <v>46021.33490740741</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D152" s="2">
-        <v>46021.68055555555</v>
+        <v>46021.68</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>195</v>
@@ -6002,16 +6002,16 @@
     </row>
     <row r="153" spans="1:10">
       <c r="A153" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B153" s="2">
-        <v>46021.30840277778</v>
+        <v>46021.25960648148</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D153" s="2">
-        <v>46021.62440972222</v>
+        <v>46021.69722222222</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>195</v>
@@ -6020,7 +6020,7 @@
         <v>212</v>
       </c>
       <c r="G153" s="2">
-        <v>18.35</v>
+        <v>23.35</v>
       </c>
       <c r="H153" s="2">
         <v>0</v>
@@ -6034,19 +6034,19 @@
     </row>
     <row r="154" spans="1:10">
       <c r="A154" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B154" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.37467592592</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D154" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.69726851852</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>212</v>
@@ -6055,7 +6055,7 @@
         <v>18.35</v>
       </c>
       <c r="H154" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I154" s="2">
         <v>0</v>
@@ -6066,16 +6066,16 @@
     </row>
     <row r="155" spans="1:10">
       <c r="A155" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B155" s="2">
-        <v>46021.33628472222</v>
+        <v>46021.29318287037</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D155" s="2">
-        <v>46021.4570949074</v>
+        <v>46021.72958333333</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>195</v>
@@ -6084,7 +6084,7 @@
         <v>212</v>
       </c>
       <c r="G155" s="2">
-        <v>18.35</v>
+        <v>21.8</v>
       </c>
       <c r="H155" s="2">
         <v>0</v>
@@ -6098,19 +6098,19 @@
     </row>
     <row r="156" spans="1:10">
       <c r="A156" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B156" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.45960648148</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D156" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.69760416666</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>212</v>
@@ -6119,7 +6119,7 @@
         <v>18.35</v>
       </c>
       <c r="H156" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I156" s="2">
         <v>0</v>
@@ -6130,16 +6130,16 @@
     </row>
     <row r="157" spans="1:10">
       <c r="A157" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B157" s="2">
-        <v>46021.25960648148</v>
+        <v>46021.32020833333</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D157" s="2">
-        <v>46021.69722222222</v>
+        <v>46021.62804398148</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>195</v>
@@ -6148,7 +6148,7 @@
         <v>212</v>
       </c>
       <c r="G157" s="2">
-        <v>23.35</v>
+        <v>18.35</v>
       </c>
       <c r="H157" s="2">
         <v>0</v>
@@ -6162,16 +6162,16 @@
     </row>
     <row r="158" spans="1:10">
       <c r="A158" s="2" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B158" s="2">
-        <v>46021.33490740741</v>
+        <v>46021.25751157408</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D158" s="2">
-        <v>46021.68</v>
+        <v>46021.6255787037</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>195</v>
@@ -6194,19 +6194,19 @@
     </row>
     <row r="159" spans="1:10">
       <c r="A159" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="B159" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.5277662037</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D159" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.68055555555</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>212</v>
@@ -6215,7 +6215,7 @@
         <v>18.35</v>
       </c>
       <c r="H159" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I159" s="2">
         <v>0</v>
@@ -6229,13 +6229,13 @@
         <v>142</v>
       </c>
       <c r="B160" s="2">
-        <v>46021.45498842592</v>
+        <v>46021.2583912037</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D160" s="2">
-        <v>46021.69689814815</v>
+        <v>46021.69268518518</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>195</v>
@@ -6261,16 +6261,16 @@
         <v>143</v>
       </c>
       <c r="B161" s="2">
-        <v>46021</v>
+        <v>46021.57956018519</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D161" s="2">
-        <v>46021</v>
+        <v>46021.90695601852</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>213</v>
@@ -6282,7 +6282,7 @@
         <v>0</v>
       </c>
       <c r="I161" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>246</v>
@@ -6290,19 +6290,19 @@
     </row>
     <row r="162" spans="1:10">
       <c r="A162" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B162" s="2">
-        <v>46021.54820601852</v>
+        <v>46021</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D162" s="2">
-        <v>46021.91363425926</v>
+        <v>46021</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>213</v>
@@ -6314,7 +6314,7 @@
         <v>0</v>
       </c>
       <c r="I162" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>246</v>
@@ -6325,13 +6325,13 @@
         <v>144</v>
       </c>
       <c r="B163" s="2">
-        <v>46021.57956018519</v>
+        <v>46021.54820601852</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D163" s="2">
-        <v>46021.90695601852</v>
+        <v>46021.91363425926</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>195</v>
@@ -6357,13 +6357,13 @@
         <v>145</v>
       </c>
       <c r="B164" s="2">
-        <v>46021.37594907408</v>
+        <v>46021.37381944444</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D164" s="2">
-        <v>46021.738125</v>
+        <v>46021.70540509259</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>195</v>
@@ -6372,7 +6372,7 @@
         <v>214</v>
       </c>
       <c r="G164" s="2">
-        <v>20.7</v>
+        <v>18.35</v>
       </c>
       <c r="H164" s="2">
         <v>0</v>
@@ -6389,13 +6389,13 @@
         <v>146</v>
       </c>
       <c r="B165" s="2">
-        <v>46021.37407407408</v>
+        <v>46021.45320601852</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D165" s="2">
-        <v>46021.71753472222</v>
+        <v>46021.63791666667</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>195</v>
@@ -6453,13 +6453,13 @@
         <v>148</v>
       </c>
       <c r="B167" s="2">
-        <v>46021.45320601852</v>
+        <v>46021.38155092593</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D167" s="2">
-        <v>46021.63791666667</v>
+        <v>46021.70805555556</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>195</v>
@@ -6468,7 +6468,7 @@
         <v>214</v>
       </c>
       <c r="G167" s="2">
-        <v>18.35</v>
+        <v>23.35</v>
       </c>
       <c r="H167" s="2">
         <v>0</v>
@@ -6485,13 +6485,13 @@
         <v>149</v>
       </c>
       <c r="B168" s="2">
-        <v>46021.37381944444</v>
+        <v>46021.37594907408</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D168" s="2">
-        <v>46021.70540509259</v>
+        <v>46021.738125</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>195</v>
@@ -6500,7 +6500,7 @@
         <v>214</v>
       </c>
       <c r="G168" s="2">
-        <v>18.35</v>
+        <v>20.7</v>
       </c>
       <c r="H168" s="2">
         <v>0</v>
@@ -6517,13 +6517,13 @@
         <v>150</v>
       </c>
       <c r="B169" s="2">
-        <v>46021.38155092593</v>
+        <v>46021.37407407408</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D169" s="2">
-        <v>46021.70805555556</v>
+        <v>46021.71753472222</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>195</v>
@@ -6532,7 +6532,7 @@
         <v>214</v>
       </c>
       <c r="G169" s="2">
-        <v>23.35</v>
+        <v>18.35</v>
       </c>
       <c r="H169" s="2">
         <v>0</v>
@@ -6613,13 +6613,13 @@
         <v>153</v>
       </c>
       <c r="B172" s="2">
-        <v>46021.68135416666</v>
+        <v>46021.37541666667</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D172" s="2">
-        <v>46021.99353009259</v>
+        <v>46021.68751157408</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>195</v>
@@ -6628,7 +6628,7 @@
         <v>216</v>
       </c>
       <c r="G172" s="2">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="H172" s="2">
         <v>0</v>
@@ -6677,13 +6677,13 @@
         <v>155</v>
       </c>
       <c r="B174" s="2">
-        <v>46021.37541666667</v>
+        <v>46021.68135416666</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D174" s="2">
-        <v>46021.68751157408</v>
+        <v>46021.99353009259</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>195</v>
@@ -6692,7 +6692,7 @@
         <v>216</v>
       </c>
       <c r="G174" s="2">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="H174" s="2">
         <v>0</v>
@@ -6709,13 +6709,13 @@
         <v>156</v>
       </c>
       <c r="B175" s="2">
-        <v>46021.37021990741</v>
+        <v>46021.33334490741</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D175" s="2">
-        <v>46021.609375</v>
+        <v>46021.70873842593</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>195</v>
@@ -6741,25 +6741,25 @@
         <v>157</v>
       </c>
       <c r="B176" s="2">
-        <v>46021.33334490741</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D176" s="2">
-        <v>46021.70873842593</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>217</v>
       </c>
       <c r="G176" s="2">
-        <v>19.6</v>
+        <v>19.25</v>
       </c>
       <c r="H176" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I176" s="2">
         <v>0</v>
@@ -6773,16 +6773,16 @@
         <v>158</v>
       </c>
       <c r="B177" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.31547453703</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D177" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.53782407408</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>217</v>
@@ -6791,7 +6791,7 @@
         <v>19.25</v>
       </c>
       <c r="H177" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I177" s="2">
         <v>0</v>
@@ -6837,13 +6837,13 @@
         <v>160</v>
       </c>
       <c r="B179" s="2">
-        <v>46021.31547453703</v>
+        <v>46021.37021990741</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D179" s="2">
-        <v>46021.53782407408</v>
+        <v>46021.609375</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>195</v>
@@ -6852,7 +6852,7 @@
         <v>217</v>
       </c>
       <c r="G179" s="2">
-        <v>19.25</v>
+        <v>19.6</v>
       </c>
       <c r="H179" s="2">
         <v>0</v>
@@ -6965,13 +6965,13 @@
         <v>164</v>
       </c>
       <c r="B183" s="2">
-        <v>46021.56255787037</v>
+        <v>46021.6838425926</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D183" s="2">
-        <v>46021.86011574074</v>
+        <v>46021.99325231482</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>195</v>
@@ -6980,7 +6980,7 @@
         <v>219</v>
       </c>
       <c r="G183" s="2">
-        <v>24.8</v>
+        <v>20.7</v>
       </c>
       <c r="H183" s="2">
         <v>0</v>
@@ -6997,13 +6997,13 @@
         <v>165</v>
       </c>
       <c r="B184" s="2">
-        <v>46021.6838425926</v>
+        <v>46021.53320601852</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D184" s="2">
-        <v>46021.99325231482</v>
+        <v>46021.69238425926</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>195</v>
@@ -7012,7 +7012,7 @@
         <v>219</v>
       </c>
       <c r="G184" s="2">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="H184" s="2">
         <v>0</v>
@@ -7029,13 +7029,13 @@
         <v>166</v>
       </c>
       <c r="B185" s="2">
-        <v>46021.575</v>
+        <v>46021.37001157407</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D185" s="2">
-        <v>46021.69486111111</v>
+        <v>46021.55858796297</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>195</v>
@@ -7058,16 +7058,16 @@
     </row>
     <row r="186" spans="1:10">
       <c r="A186" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B186" s="2">
-        <v>46021.37247685185</v>
+        <v>46021.575</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D186" s="2">
-        <v>46021.59961805555</v>
+        <v>46021.69486111111</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>195</v>
@@ -7093,13 +7093,13 @@
         <v>167</v>
       </c>
       <c r="B187" s="2">
-        <v>46021.61828703704</v>
+        <v>46021.37247685185</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D187" s="2">
-        <v>46021.68643518518</v>
+        <v>46021.59961805555</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>195</v>
@@ -7122,16 +7122,16 @@
     </row>
     <row r="188" spans="1:10">
       <c r="A188" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B188" s="2">
-        <v>46021.37001157407</v>
+        <v>46021.61828703704</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D188" s="2">
-        <v>46021.55858796297</v>
+        <v>46021.68643518518</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>195</v>
@@ -7157,13 +7157,13 @@
         <v>168</v>
       </c>
       <c r="B189" s="2">
-        <v>46021.69841435185</v>
+        <v>46021.37746527778</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D189" s="2">
-        <v>46021.99342592592</v>
+        <v>46021.63792824074</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>195</v>
@@ -7172,7 +7172,7 @@
         <v>219</v>
       </c>
       <c r="G189" s="2">
-        <v>19.65</v>
+        <v>21.45</v>
       </c>
       <c r="H189" s="2">
         <v>0</v>
@@ -7189,13 +7189,13 @@
         <v>169</v>
       </c>
       <c r="B190" s="2">
-        <v>46021.33607638889</v>
+        <v>46021.40107638889</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D190" s="2">
-        <v>46021.51090277778</v>
+        <v>46021.53712962963</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>195</v>
@@ -7204,7 +7204,7 @@
         <v>219</v>
       </c>
       <c r="G190" s="2">
-        <v>21.2</v>
+        <v>24.8</v>
       </c>
       <c r="H190" s="2">
         <v>0</v>
@@ -7218,16 +7218,16 @@
     </row>
     <row r="191" spans="1:10">
       <c r="A191" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B191" s="2">
-        <v>46021.40107638889</v>
+        <v>46021.56255787037</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D191" s="2">
-        <v>46021.53712962963</v>
+        <v>46021.86011574074</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>195</v>
@@ -7253,13 +7253,13 @@
         <v>170</v>
       </c>
       <c r="B192" s="2">
-        <v>46021.37746527778</v>
+        <v>46021.69841435185</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D192" s="2">
-        <v>46021.63792824074</v>
+        <v>46021.99342592592</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>195</v>
@@ -7268,7 +7268,7 @@
         <v>219</v>
       </c>
       <c r="G192" s="2">
-        <v>21.45</v>
+        <v>19.65</v>
       </c>
       <c r="H192" s="2">
         <v>0</v>
@@ -7282,16 +7282,16 @@
     </row>
     <row r="193" spans="1:10">
       <c r="A193" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B193" s="2">
-        <v>46021.53320601852</v>
+        <v>46021.33607638889</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D193" s="2">
-        <v>46021.69238425926</v>
+        <v>46021.51090277778</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>195</v>
@@ -7317,13 +7317,13 @@
         <v>171</v>
       </c>
       <c r="B194" s="2">
-        <v>46021.37978009259</v>
+        <v>46021.31883101852</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D194" s="2">
-        <v>46021.68116898148</v>
+        <v>46021.69268518518</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>195</v>
@@ -7332,7 +7332,7 @@
         <v>220</v>
       </c>
       <c r="G194" s="2">
-        <v>26.8</v>
+        <v>26.5</v>
       </c>
       <c r="H194" s="2">
         <v>0</v>
@@ -7349,25 +7349,25 @@
         <v>172</v>
       </c>
       <c r="B195" s="2">
-        <v>46021.5</v>
+        <v>46021.32467592593</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D195" s="2">
-        <v>46021.5</v>
+        <v>46021.60603009259</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>220</v>
       </c>
       <c r="G195" s="2">
-        <v>0</v>
+        <v>22.75</v>
       </c>
       <c r="H195" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I195" s="2">
         <v>0</v>
@@ -7381,13 +7381,13 @@
         <v>173</v>
       </c>
       <c r="B196" s="2">
-        <v>46021.31934027778</v>
+        <v>46021.37978009259</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D196" s="2">
-        <v>46021.6910300926</v>
+        <v>46021.68116898148</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>195</v>
@@ -7396,7 +7396,7 @@
         <v>220</v>
       </c>
       <c r="G196" s="2">
-        <v>26.45</v>
+        <v>26.8</v>
       </c>
       <c r="H196" s="2">
         <v>0</v>
@@ -7413,25 +7413,25 @@
         <v>174</v>
       </c>
       <c r="B197" s="2">
-        <v>46021.31883101852</v>
+        <v>46021.5</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D197" s="2">
-        <v>46021.69268518518</v>
+        <v>46021.5</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>220</v>
       </c>
       <c r="G197" s="2">
-        <v>26.5</v>
+        <v>0</v>
       </c>
       <c r="H197" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I197" s="2">
         <v>0</v>
@@ -7445,13 +7445,13 @@
         <v>175</v>
       </c>
       <c r="B198" s="2">
-        <v>46021.32467592593</v>
+        <v>46021.31934027778</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D198" s="2">
-        <v>46021.60603009259</v>
+        <v>46021.6910300926</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>195</v>
@@ -7460,7 +7460,7 @@
         <v>220</v>
       </c>
       <c r="G198" s="2">
-        <v>22.75</v>
+        <v>26.45</v>
       </c>
       <c r="H198" s="2">
         <v>0</v>
@@ -7509,13 +7509,13 @@
         <v>177</v>
       </c>
       <c r="B200" s="2">
-        <v>46021.36476851852</v>
+        <v>46021.34954861111</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D200" s="2">
-        <v>46021.71784722222</v>
+        <v>46021.52262731481</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>195</v>
@@ -7573,13 +7573,13 @@
         <v>179</v>
       </c>
       <c r="B202" s="2">
-        <v>46021.32997685186</v>
+        <v>46021.36476851852</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D202" s="2">
-        <v>46021.73337962963</v>
+        <v>46021.71784722222</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>195</v>
@@ -7588,7 +7588,7 @@
         <v>222</v>
       </c>
       <c r="G202" s="2">
-        <v>31.64</v>
+        <v>30.78</v>
       </c>
       <c r="H202" s="2">
         <v>0</v>
@@ -7637,13 +7637,13 @@
         <v>181</v>
       </c>
       <c r="B204" s="2">
-        <v>46021.34954861111</v>
+        <v>46021.32997685186</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D204" s="2">
-        <v>46021.52262731481</v>
+        <v>46021.73337962963</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>195</v>
@@ -7652,7 +7652,7 @@
         <v>222</v>
       </c>
       <c r="G204" s="2">
-        <v>30.78</v>
+        <v>31.64</v>
       </c>
       <c r="H204" s="2">
         <v>0</v>
@@ -7733,13 +7733,13 @@
         <v>184</v>
       </c>
       <c r="B207" s="2">
-        <v>46021.48813657407</v>
+        <v>46021.57773148148</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D207" s="2">
-        <v>46021.52363425926</v>
+        <v>46021.6353125</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>195</v>
@@ -7748,7 +7748,7 @@
         <v>224</v>
       </c>
       <c r="G207" s="2">
-        <v>23</v>
+        <v>26.75</v>
       </c>
       <c r="H207" s="2">
         <v>0</v>
@@ -7762,16 +7762,16 @@
     </row>
     <row r="208" spans="1:10">
       <c r="A208" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B208" s="2">
-        <v>46021.56311342592</v>
+        <v>46021.48813657407</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D208" s="2">
-        <v>46021.67813657408</v>
+        <v>46021.52363425926</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>195</v>
@@ -7797,13 +7797,13 @@
         <v>185</v>
       </c>
       <c r="B209" s="2">
-        <v>46021.30827546296</v>
+        <v>46021.56311342592</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D209" s="2">
-        <v>46021.71158564815</v>
+        <v>46021.67813657408</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>195</v>
@@ -7812,7 +7812,7 @@
         <v>224</v>
       </c>
       <c r="G209" s="2">
-        <v>21.4</v>
+        <v>23</v>
       </c>
       <c r="H209" s="2">
         <v>0</v>
@@ -7826,7 +7826,7 @@
     </row>
     <row r="210" spans="1:10">
       <c r="A210" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B210" s="2">
         <v>46021.29733796296</v>
@@ -7861,13 +7861,13 @@
         <v>186</v>
       </c>
       <c r="B211" s="2">
-        <v>46021.57773148148</v>
+        <v>46021.30827546296</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D211" s="2">
-        <v>46021.6353125</v>
+        <v>46021.71158564815</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>195</v>
@@ -7876,7 +7876,7 @@
         <v>224</v>
       </c>
       <c r="G211" s="2">
-        <v>26.75</v>
+        <v>21.4</v>
       </c>
       <c r="H211" s="2">
         <v>0</v>
